--- a/DataRepo/tests/data/blank_samples/blanks1/blank_sample_skip_study.xlsx
+++ b/DataRepo/tests/data/blank_samples/blanks1/blank_sample_skip_study.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/data/tests/blank_samples/blanks1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/tests/data/blank_samples/blanks1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D2EF11-B0D0-704E-B7CD-6F46DA4978C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432BAA67-267C-C348-9934-530155440436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16480" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16480" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study" sheetId="9" r:id="rId1"/>
@@ -1781,13 +1781,13 @@
     <t>skip</t>
   </si>
   <si>
-    <t>DataRepo/data/tests/blank_samples/blanks1/accucor_with_blank.xlsx</t>
-  </si>
-  <si>
     <t>accucor_with_blank.xlsx</t>
   </si>
   <si>
     <t>ob/ob homozygous mice were fasted</t>
+  </si>
+  <si>
+    <t>DataRepo/tests/data/blank_samples/blanks1/accucor_with_blank.xlsx</t>
   </si>
 </sst>
 </file>
@@ -22083,7 +22083,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>29</v>
@@ -22138,7 +22138,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>30</v>
@@ -22152,7 +22152,7 @@
         <v>78</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>30</v>
@@ -22231,7 +22231,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
